--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="R5" t="n">
-        <v>5.01</v>
+        <v>3.62</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46112.79166666666</v>
+        <v>46112.77083333334</v>
       </c>
     </row>
     <row r="6">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>3.62</v>
+        <v>5.01</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -810,124 +810,124 @@
         <v>2.7</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1007,124 +1007,124 @@
         <v>4.04</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -1401,124 +1401,124 @@
         <v>3.62</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -1204,124 +1204,124 @@
         <v>4.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
         <v>3.16</v>
@@ -852,13 +852,13 @@
         <v>1.97</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AH2" t="n">
         <v>1.31</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.08</v>
@@ -1001,25 +1001,25 @@
         <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.93</v>
+        <v>3.52</v>
       </c>
       <c r="R3" t="n">
-        <v>4.04</v>
+        <v>3.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="X3" t="n">
         <v>2.36</v>
@@ -1028,49 +1028,49 @@
         <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AA3" t="n">
         <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
         <v>1.16</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AM3" t="n">
         <v>1.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>1.36</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AS3" t="n">
         <v>2.63</v>
@@ -1097,16 +1097,16 @@
         <v>2.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AY3" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="BA3" t="n">
         <v>2.32</v>
@@ -1115,16 +1115,16 @@
         <v>1.15</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BD3" t="n">
         <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1198,10 +1198,10 @@
         <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>2.24</v>
@@ -1297,7 +1297,7 @@
         <v>1.87</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AY4" t="n">
         <v>1.33</v>
@@ -1306,7 +1306,7 @@
         <v>1.32</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BB4" t="n">
         <v>1.18</v>
@@ -1401,13 +1401,13 @@
         <v>3.62</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="V5" t="n">
         <v>1.49</v>
@@ -1416,7 +1416,7 @@
         <v>2.41</v>
       </c>
       <c r="X5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Y5" t="n">
         <v>1.28</v>
@@ -1428,7 +1428,7 @@
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
         <v>1.38</v>
@@ -1437,16 +1437,16 @@
         <v>2.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AF5" t="n">
         <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
         <v>9.5</v>
@@ -1455,10 +1455,10 @@
         <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AM5" t="n">
         <v>1.33</v>
@@ -1473,31 +1473,31 @@
         <v>1.19</v>
       </c>
       <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.34</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.95</v>
@@ -1506,19 +1506,19 @@
         <v>2.07</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BD5" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="BE5" t="n">
         <v>1.48</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>5.01</v>
+        <v>4.6</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="S3" t="n">
         <v>2.3</v>
@@ -1198,7 +1198,7 @@
         <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R4" t="n">
         <v>4</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
         <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="S3" t="n">
         <v>2.3</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="S4" t="n">
         <v>2.24</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="R6" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -807,73 +807,73 @@
         <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S2" t="n">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="X2" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="AE2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.88</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG2" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -885,13 +885,13 @@
         <v>1.66</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AU2" t="n">
         <v>2.7</v>
@@ -903,10 +903,10 @@
         <v>1.64</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.9</v>
@@ -915,19 +915,19 @@
         <v>2.14</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.98</v>
+        <v>3.85</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R3" t="n">
         <v>3.4</v>
       </c>
-      <c r="R3" t="n">
-        <v>3.82</v>
-      </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>4.3</v>
+        <v>3.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="X3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.15</v>
+        <v>5.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>2.32</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,88 +1195,88 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
         <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.03</v>
       </c>
-      <c r="AG4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
         <v>1.79</v>
@@ -1285,43 +1285,43 @@
         <v>2.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AW4" t="n">
         <v>1.87</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.32</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.05</v>
+        <v>3.66</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -1401,25 +1401,25 @@
         <v>3.62</v>
       </c>
       <c r="S5" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.15</v>
+        <v>3.89</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
         <v>8.5</v>
@@ -1428,7 +1428,7 @@
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
         <v>1.38</v>
@@ -1437,73 +1437,73 @@
         <v>2.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
         <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.45</v>
+        <v>4.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM5" t="n">
         <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.65</v>
+        <v>3.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="BB5" t="n">
         <v>1.3</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -801,34 +801,34 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
         <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z2" t="n">
         <v>6.4</v>
@@ -843,19 +843,19 @@
         <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI2" t="n">
         <v>5.8</v>
@@ -873,46 +873,46 @@
         <v>1.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AS2" t="n">
         <v>2.39</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AX2" t="n">
         <v>1.51</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BB2" t="n">
         <v>1.2</v>
@@ -1004,7 +1004,7 @@
         <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="S3" t="n">
         <v>2.55</v>
@@ -1013,22 +1013,22 @@
         <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="X3" t="n">
         <v>2.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA3" t="n">
         <v>1.07</v>
@@ -1043,43 +1043,43 @@
         <v>3.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL3" t="n">
         <v>2.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AR3" t="n">
         <v>2.02</v>
@@ -1088,28 +1088,28 @@
         <v>2.63</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="AW3" t="n">
         <v>1.68</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="BB3" t="n">
         <v>1.18</v>
@@ -1124,7 +1124,7 @@
         <v>1.78</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
         <v>3.4</v>
@@ -1207,10 +1207,10 @@
         <v>2.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="V4" t="n">
         <v>1.39</v>
@@ -1225,13 +1225,13 @@
         <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="AA4" t="n">
         <v>1.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
         <v>1.25</v>
@@ -1240,7 +1240,7 @@
         <v>3.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
         <v>1.85</v>
@@ -1261,49 +1261,49 @@
         <v>1.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AM4" t="n">
         <v>1.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.88</v>
+        <v>3.36</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BA4" t="n">
         <v>3.85</v>
@@ -1312,13 +1312,13 @@
         <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BD4" t="n">
         <v>3.66</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BF4" t="n">
         <v>1.15</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="V2" t="n">
         <v>1.39</v>
@@ -831,34 +831,34 @@
         <v>1.39</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AH2" t="n">
         <v>1.28</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.07</v>
@@ -867,13 +867,13 @@
         <v>1.76</v>
       </c>
       <c r="AL2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AM2" t="n">
         <v>1.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -882,7 +882,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AR2" t="n">
         <v>2.14</v>
@@ -897,7 +897,7 @@
         <v>3.12</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AW2" t="n">
         <v>1.84</v>
@@ -915,16 +915,16 @@
         <v>2.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
         <v>1.16</v>
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
         <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="T3" t="n">
         <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
         <v>1.35</v>
@@ -1022,10 +1022,10 @@
         <v>2.94</v>
       </c>
       <c r="X3" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z3" t="n">
         <v>5.5</v>
@@ -1043,22 +1043,22 @@
         <v>3.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AH3" t="n">
         <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
         <v>1.63</v>
@@ -1070,37 +1070,37 @@
         <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.48</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AT3" t="n">
         <v>2.95</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="AV3" t="n">
         <v>2.46</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AY3" t="n">
         <v>1.35</v>
@@ -1115,16 +1115,16 @@
         <v>1.18</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BD3" t="n">
         <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="S4" t="n">
         <v>2.3</v>
@@ -1210,7 +1210,7 @@
         <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="V4" t="n">
         <v>1.39</v>
@@ -1219,13 +1219,13 @@
         <v>2.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.05</v>
@@ -1240,34 +1240,34 @@
         <v>3.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AF4" t="n">
         <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AH4" t="n">
         <v>1.32</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AM4" t="n">
         <v>1.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>1.35</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AT4" t="n">
         <v>3.36</v>
@@ -1291,19 +1291,19 @@
         <v>2.95</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
         <v>1.26</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BA4" t="n">
         <v>3.85</v>
@@ -1321,7 +1321,7 @@
         <v>1.67</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -1392,19 +1392,19 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>3.62</v>
+        <v>3.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
         <v>3.89</v>
@@ -1413,13 +1413,13 @@
         <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="X5" t="n">
         <v>3.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
         <v>8.5</v>
@@ -1440,7 +1440,7 @@
         <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
         <v>4.1</v>
@@ -1500,10 +1500,10 @@
         <v>1.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BB5" t="n">
         <v>1.3</v>
@@ -1592,10 +1592,10 @@
         <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="R6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="Q2" t="n">
         <v>3.2</v>
@@ -810,13 +810,13 @@
         <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="T2" t="n">
         <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="V2" t="n">
         <v>1.39</v>
@@ -831,7 +831,7 @@
         <v>1.39</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="AA2" t="n">
         <v>1.04</v>
@@ -870,19 +870,19 @@
         <v>2.06</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AR2" t="n">
         <v>2.14</v>
@@ -894,22 +894,22 @@
         <v>3.15</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AW2" t="n">
         <v>1.84</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AY2" t="n">
         <v>1.31</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="BA2" t="n">
         <v>2.2</v>
@@ -924,7 +924,7 @@
         <v>3.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="BF2" t="n">
         <v>1.16</v>
@@ -998,85 +998,85 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="S3" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>3.39</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
         <v>5.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
         <v>2.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.48</v>
@@ -1085,46 +1085,46 @@
         <v>1.81</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AT3" t="n">
         <v>2.95</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="AV3" t="n">
         <v>2.46</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AY3" t="n">
         <v>1.35</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,52 +1195,52 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="V4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.39</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.43</v>
-      </c>
       <c r="Z4" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
         <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD4" t="n">
         <v>3.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
         <v>1.85</v>
@@ -1249,10 +1249,10 @@
         <v>3.12</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.07</v>
@@ -1261,13 +1261,13 @@
         <v>1.84</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,28 +1276,28 @@
         <v>1.35</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AT4" t="n">
         <v>3.36</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AY4" t="n">
         <v>1.26</v>
@@ -1312,13 +1312,13 @@
         <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="BD4" t="n">
         <v>3.66</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BF4" t="n">
         <v>1.16</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
         <v>3.15</v>
@@ -1401,22 +1401,22 @@
         <v>3.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
         <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>3.89</v>
+        <v>4.5</v>
       </c>
       <c r="V5" t="n">
         <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Y5" t="n">
         <v>1.28</v>
@@ -1425,13 +1425,13 @@
         <v>8.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
         <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AD5" t="n">
         <v>2.62</v>
@@ -1440,13 +1440,13 @@
         <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
         <v>4.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" t="n">
         <v>8.300000000000001</v>
@@ -1455,7 +1455,7 @@
         <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL5" t="n">
         <v>1.76</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AS5" t="n">
         <v>2.14</v>
@@ -1488,10 +1488,10 @@
         <v>3.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AX5" t="n">
         <v>1.62</v>
@@ -1500,7 +1500,7 @@
         <v>1.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="BA5" t="n">
         <v>2.68</v>
@@ -1518,7 +1518,7 @@
         <v>1.48</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>5.16</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="T2" t="n">
         <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="V2" t="n">
         <v>1.39</v>
@@ -840,7 +840,7 @@
         <v>1.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD2" t="n">
         <v>3.3</v>
@@ -855,13 +855,13 @@
         <v>3.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
         <v>5.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
         <v>1.76</v>
@@ -873,7 +873,7 @@
         <v>1.34</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -882,31 +882,31 @@
         <v>1.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.85</v>
@@ -1004,34 +1004,34 @@
         <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="S3" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="X3" t="n">
         <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
@@ -1040,34 +1040,34 @@
         <v>1.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AE3" t="n">
         <v>1.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>2.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
         <v>1.75</v>
@@ -1103,10 +1103,10 @@
         <v>1.57</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="BA3" t="n">
         <v>2.3</v>
@@ -1115,16 +1115,16 @@
         <v>1.16</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1198,16 +1198,16 @@
         <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>4.4</v>
+        <v>4.88</v>
       </c>
       <c r="S4" t="n">
         <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
         <v>5.25</v>
@@ -1216,16 +1216,16 @@
         <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="X4" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="Y4" t="n">
         <v>1.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="AA4" t="n">
         <v>1.09</v>
@@ -1240,67 +1240,67 @@
         <v>3.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AF4" t="n">
         <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AH4" t="n">
         <v>1.28</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AM4" t="n">
         <v>1.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="AU4" t="n">
         <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.38</v>
@@ -1309,16 +1309,16 @@
         <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC4" t="n">
         <v>2.11</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
         <v>1.16</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -1392,16 +1392,16 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
         <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>3.49</v>
+        <v>3.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
         <v>1.92</v>
@@ -1410,13 +1410,13 @@
         <v>4.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="X5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Y5" t="n">
         <v>1.28</v>
@@ -1425,28 +1425,28 @@
         <v>8.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
         <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AD5" t="n">
         <v>2.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
         <v>4.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
         <v>8.300000000000001</v>
@@ -1455,10 +1455,10 @@
         <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AM5" t="n">
         <v>1.33</v>
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.35</v>
@@ -1488,10 +1488,10 @@
         <v>3.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AX5" t="n">
         <v>1.62</v>
@@ -1512,13 +1512,13 @@
         <v>2.44</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="S2" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
         <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
         <v>2.77</v>
@@ -834,19 +834,19 @@
         <v>6.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
         <v>3.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
         <v>1.9</v>
@@ -855,22 +855,22 @@
         <v>3.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AI2" t="n">
         <v>5.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AN2" t="n">
         <v>1.46</v>
@@ -882,43 +882,43 @@
         <v>1.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="AT2" t="n">
         <v>3.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.85</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BD2" t="n">
         <v>3.75</v>
@@ -1001,88 +1001,88 @@
         <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>3.55</v>
+        <v>4.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.94</v>
+        <v>4.13</v>
       </c>
       <c r="AE3" t="n">
         <v>1.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AH3" t="n">
         <v>1.41</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
         <v>1.57</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AM3" t="n">
         <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AS3" t="n">
         <v>2.26</v>
@@ -1103,25 +1103,25 @@
         <v>1.57</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="BB3" t="n">
         <v>1.16</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BD3" t="n">
         <v>4.33</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BF3" t="n">
         <v>1.23</v>
@@ -1195,40 +1195,40 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
-        <v>4.88</v>
+        <v>4.7</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
         <v>1.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
         <v>1.06</v>
@@ -1237,85 +1237,85 @@
         <v>1.26</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AH4" t="n">
         <v>1.28</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.88</v>
+        <v>3.36</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AY4" t="n">
         <v>1.34</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="BE4" t="n">
         <v>1.68</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -1392,34 +1392,34 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>3.63</v>
+        <v>3.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U5" t="n">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="X5" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
         <v>8.5</v>
@@ -1434,49 +1434,49 @@
         <v>1.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.1</v>
+        <v>4.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AS5" t="n">
         <v>2.14</v>
@@ -1488,10 +1488,10 @@
         <v>3.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AX5" t="n">
         <v>1.62</v>
@@ -1500,25 +1500,25 @@
         <v>1.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -787,39 +787,39 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="T2" t="n">
         <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.9</v>
+        <v>3.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
         <v>2.77</v>
@@ -834,7 +834,7 @@
         <v>6.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
@@ -843,13 +843,13 @@
         <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG2" t="n">
         <v>3.12</v>
@@ -858,7 +858,7 @@
         <v>1.28</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.9</v>
+        <v>7.15</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.07</v>
@@ -870,43 +870,43 @@
         <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.85</v>
@@ -918,16 +918,16 @@
         <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="BD2" t="n">
         <v>3.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -987,90 +987,90 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>4.04</v>
+        <v>4.53</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="X3" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.4</v>
+        <v>5.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.13</v>
+        <v>3.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1079,28 +1079,28 @@
         <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AT3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU3" t="n">
         <v>2.95</v>
       </c>
-      <c r="AU3" t="n">
-        <v>3.32</v>
-      </c>
       <c r="AV3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AY3" t="n">
         <v>1.35</v>
@@ -1109,22 +1109,22 @@
         <v>1.75</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="R4" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>5.46</v>
+        <v>6.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.32</v>
       </c>
       <c r="BA4" t="n">
         <v>3.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.66</v>
+        <v>4.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>

--- a/jogos_2026-03-31.xlsx
+++ b/jogos_2026-03-31.xlsx
@@ -1166,32 +1166,32 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1381,39 +1381,39 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="S5" t="n">
         <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U5" t="n">
-        <v>4.88</v>
+        <v>4.72</v>
       </c>
       <c r="V5" t="n">
         <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="X5" t="n">
         <v>3.22</v>
@@ -1425,7 +1425,7 @@
         <v>8.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
         <v>1.04</v>
@@ -1434,19 +1434,19 @@
         <v>1.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
         <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.37</v>
+        <v>4.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
         <v>8.1</v>
@@ -1464,7 +1464,7 @@
         <v>1.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AR5" t="n">
         <v>1.7</v>
@@ -1500,7 +1500,7 @@
         <v>1.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
         <v>2.75</v>
@@ -1509,13 +1509,13 @@
         <v>1.29</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BF5" t="n">
         <v>1.08</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="R6" t="n">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="S6" t="n">
         <v>2.31</v>
@@ -1607,19 +1607,19 @@
         <v>6.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="X6" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.01</v>
@@ -1628,25 +1628,25 @@
         <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AD6" t="n">
         <v>2.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AH6" t="n">
         <v>1.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.01</v>
@@ -1658,10 +1658,10 @@
         <v>1.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,37 +1670,37 @@
         <v>1.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
         <v>3.15</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.31</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="BB6" t="n">
         <v>1.31</v>
@@ -1715,7 +1715,7 @@
         <v>1.47</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
